--- a/templates/000_pm_suite/01_프로젝트 관리/06_조직관리/프로젝트명_투입인력 프로필_20230531.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/06_조직관리/프로젝트명_투입인력 프로필_20230531.xlsx
@@ -523,7 +523,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-17] SyncGuard AI 투입인력 프로필 및 KOSA 기술등급·경력 명세서 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-17] SyncFlow AI 투입인력 프로필 및 KOSA 기술등급·경력 명세서 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>React 18 / TypeScript 기반 AI 문서 심의 뷰어 및 어드민 포털 개발</t>
+          <t>React 18 / TypeScript 기반 AI 문서 검증 뷰어 및 어드민 포털 개발</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>대기업 ERP/PLM/마케팅 시스템 REST API 및 SSO 통합인증 연계</t>
+          <t>대기업 ERP/PLM/구매조달 시스템 REST API 및 SSO 통합인증 연계</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Spring Batch 기반 대용량 전성분 마스터 일배치 동기화 구현</t>
+          <t>Spring Batch 기반 대용량 자재BOM 마스터 일배치 동기화 구현</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>화장품·의약품 표시광고 금지어 정규식 룰셋 및 골든셋 자동 평가기 개발</t>
+          <t>전장부품·불공정특약 계약·기술규격 독소조항 정규식 룰셋 및 골든셋 자동 평가기 개발</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
